--- a/excel/bosses.xlsx
+++ b/excel/bosses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GODOT\Project\BOOOM202604\Booom202604\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1934F511-579E-4354-B0A3-982AB1099FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E33A2D-EB42-48B8-8952-939D95F917AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="1080" windowWidth="19965" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="19965" windowHeight="15119" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bosses" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -47,197 +47,6 @@
   </si>
   <si>
     <t>独角仙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>BOSS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">技能范围定义（生效范围）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">1: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>以</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>格为中心，半径为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">格的圆形
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">2: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>以</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>格为中心，半径为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">格的圆形
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：六边形任意直线（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">种方向）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：全地图</t>
-    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -314,10 +123,6 @@
       </rPr>
       <t>：全地图任意位置</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在规定范围内生成迷雾</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -325,6 +130,374 @@
 1：在技能范围内生成迷雾
 2：使所有技能范围内的monster属性值增加1
 3：使所有技能范围内的monster属性值反转（即力量变成魔法，魔法变成力量）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在规定范围内生成迷雾，并在迷雾中随机刷新1个怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>怪物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>配置</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在规定范围内生成迷雾，并在迷雾中随机刷新2个怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2001,2002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哥布林国王</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>独角仙国王</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>BOSS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">技能范围定义（生效范围）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>格为中心，半径为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">格的圆形
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>格为中心，半径为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">格的圆形
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：六边形任意直线，从地图的一个边界到另一个边界（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">种方向）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">：全地图
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：六边形任意一个方向的直线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">格
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：六边形任意一个方向的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>条直线，从地图的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个边界到另一个边界</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在规定范围内生成迷雾，并在迷雾中随机刷新3个怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巫妖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大巫妖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3001,3002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在范围内所有格子上生成迷雾，并在迷雾中随机位置生成4个怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在范围内随机10个格子上生成迷雾，并在迷雾中随机位置生成4个怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4001,4002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -332,7 +505,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -349,6 +522,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -373,7 +553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -382,6 +562,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -684,18 +866,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="2" max="2" width="12.3984375" customWidth="1"/>
     <col min="3" max="3" width="16.9296875" customWidth="1"/>
     <col min="4" max="4" width="14.9296875" customWidth="1"/>
     <col min="5" max="5" width="17.19921875" customWidth="1"/>
     <col min="6" max="6" width="37.796875" customWidth="1"/>
     <col min="7" max="7" width="32.265625" customWidth="1"/>
-    <col min="8" max="8" width="27.53125" customWidth="1"/>
+    <col min="8" max="8" width="41.796875" customWidth="1"/>
+    <col min="9" max="9" width="10" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="149.65" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="131.65" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -712,16 +896,19 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -738,33 +925,162 @@
         <v>1</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>5</v>
+      </c>
       <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I2" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>2</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/excel/bosses.xlsx
+++ b/excel/bosses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GODOT\Project\BOOOM202604\Booom202604\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E33A2D-EB42-48B8-8952-939D95F917AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8A4647-DC99-4A8C-B3E5-BD010218CBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="19965" windowHeight="15119" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4507" yWindow="1080" windowWidth="19965" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bosses" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>ID</t>
   </si>
@@ -133,10 +133,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在规定范围内生成迷雾，并在迷雾中随机刷新1个怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -166,10 +162,6 @@
       </rPr>
       <t>配置</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在规定范围内生成迷雾，并在迷雾中随机刷新2个怪物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -473,10 +465,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在规定范围内生成迷雾，并在迷雾中随机刷新3个怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>巫妖</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -489,15 +477,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>在范围内所有格子上生成迷雾，并在迷雾中随机位置生成4个怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在范围内随机10个格子上生成迷雾，并在迷雾中随机位置生成4个怪物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>4001,4002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>BOSS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图片</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在1格圆形范围内生成迷雾，并在迷雾中随机刷新1个怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在3格范围内生成迷雾，并在迷雾中随机刷新1个怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在任意2条直线范围内生成迷雾，并在迷雾中随机刷新2个怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在任意1条直线范围内生成迷雾，并在迷雾中随机刷新2个怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在2格圆形范围内随机10个格子上生成迷雾，并在迷雾中随机位置生成3个怪物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在2格圆形范围内所有格子上生成迷雾，并在迷雾中随机位置生成3个怪物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -866,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12.3984375" customWidth="1"/>
@@ -879,7 +899,7 @@
     <col min="9" max="9" width="10" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="131.65" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="131.65" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -899,16 +919,19 @@
         <v>7</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -931,18 +954,21 @@
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="J2" s="1">
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -960,13 +986,16 @@
         <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -989,18 +1018,21 @@
         <v>3</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>1004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -1018,18 +1050,21 @@
         <v>6</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>19</v>
+      <c r="J5">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>1005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -1047,18 +1082,21 @@
         <v>2</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>1006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1076,10 +1114,13 @@
         <v>2</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/excel/bosses.xlsx
+++ b/excel/bosses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GODOT\Project\BOOOM202604\Booom202604\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8A4647-DC99-4A8C-B3E5-BD010218CBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1115FC-5C56-46F4-8C43-25B15A9B0823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4507" yWindow="1080" windowWidth="19965" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="19965" windowHeight="15119" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bosses" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -519,13 +519,156 @@
   <si>
     <t>在2格圆形范围内所有格子上生成迷雾，并在迷雾中随机位置生成3个怪物</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能图标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Art/Icon/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>301</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.png</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Art/Icon/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>302.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>res://Art/Icon/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>303.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>res://Art/Icon/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>304.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>res://Art/Icon/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>305.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>res://Art/Icon/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>306.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t/>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -552,6 +695,19 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -573,7 +729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -584,6 +740,7 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -886,240 +1043,261 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="12.3984375" customWidth="1"/>
-    <col min="3" max="3" width="16.9296875" customWidth="1"/>
-    <col min="4" max="4" width="14.9296875" customWidth="1"/>
-    <col min="5" max="5" width="17.19921875" customWidth="1"/>
-    <col min="6" max="6" width="37.796875" customWidth="1"/>
-    <col min="7" max="7" width="32.265625" customWidth="1"/>
-    <col min="8" max="8" width="41.796875" customWidth="1"/>
-    <col min="9" max="9" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.3984375" customWidth="1"/>
+    <col min="4" max="4" width="16.9296875" customWidth="1"/>
+    <col min="5" max="5" width="14.9296875" customWidth="1"/>
+    <col min="6" max="6" width="17.19921875" customWidth="1"/>
+    <col min="7" max="7" width="37.796875" customWidth="1"/>
+    <col min="8" max="8" width="32.265625" customWidth="1"/>
+    <col min="9" max="9" width="41.796875" customWidth="1"/>
+    <col min="10" max="10" width="10" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="131.65" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="131.65" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1001</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2">
         <v>5</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>2</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1002</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3">
         <v>5</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>1003</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4">
         <v>7</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>1004</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
         <v>6</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>6</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>1005</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6">
         <v>7</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>1</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.65" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" ht="14.65" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>1006</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7">
         <v>6</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>3</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>1</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>1</v>
       </c>
     </row>
